--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00890B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00890B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7214D1F-2417-482E-A558-ECC6EB4650DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CBFE70F-56E8-44F8-A78E-8B381DFDA7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{50DE345F-9FDE-45C3-861D-A5767A7E518F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CF144B85-CD66-4E7C-ACD5-1EABC9248C9B}"/>
   </bookViews>
   <sheets>
     <sheet name="00890B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1621,25 +1621,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8BD3D8-45EC-4D16-89B5-572D824FB6F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EEBA201-95A4-4010-A87D-929AD8885BD8}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1793,7 +1793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1873,7 +1873,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2487,7 +2487,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2023</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>26</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>26</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>26</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2022</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>4.66</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>26</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>26</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2021</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>26</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="51" t="s">
         <v>78</v>
       </c>
